--- a/data/tickets.xlsx
+++ b/data/tickets.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,6 +1059,80 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/04/2026 13:42:35</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Zoo Picasso</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Y3806548Q</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>prueba</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/04/2026 13:42:35</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Zoo Picasso</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Y3806548Q</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>prueba1</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
